--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246445</v>
+        <v>121246612</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>90468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517546</v>
+        <v>517537</v>
       </c>
       <c r="R2" t="n">
-        <v>6706147</v>
+        <v>6706121</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246704</v>
+        <v>121246733</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517530</v>
+        <v>517571</v>
       </c>
       <c r="R3" t="n">
-        <v>6706114</v>
+        <v>6706187</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -892,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246723</v>
+        <v>121246653</v>
       </c>
       <c r="B4" t="n">
-        <v>90687</v>
+        <v>97998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517560</v>
+        <v>517528</v>
       </c>
       <c r="R4" t="n">
-        <v>6706160</v>
+        <v>6706125</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246612</v>
+        <v>121246696</v>
       </c>
       <c r="B5" t="n">
-        <v>90458</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1045,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517537</v>
+        <v>517523</v>
       </c>
       <c r="R5" t="n">
-        <v>6706121</v>
+        <v>6706120</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246552</v>
+        <v>121246714</v>
       </c>
       <c r="B6" t="n">
-        <v>97025</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,31 +1124,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517527</v>
+        <v>517557</v>
       </c>
       <c r="R6" t="n">
-        <v>6706134</v>
+        <v>6706166</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246653</v>
+        <v>121246723</v>
       </c>
       <c r="B7" t="n">
-        <v>97988</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,35 +1234,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517528</v>
+        <v>517560</v>
       </c>
       <c r="R7" t="n">
-        <v>6706125</v>
+        <v>6706160</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1326,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246733</v>
+        <v>121246552</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>97035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,30 +1340,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517571</v>
+        <v>517527</v>
       </c>
       <c r="R8" t="n">
-        <v>6706187</v>
+        <v>6706134</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1432,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246696</v>
+        <v>121246704</v>
       </c>
       <c r="B9" t="n">
-        <v>90973</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,28 +1451,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1479,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517523</v>
+        <v>517530</v>
       </c>
       <c r="R9" t="n">
-        <v>6706120</v>
+        <v>6706114</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246714</v>
+        <v>121246445</v>
       </c>
       <c r="B10" t="n">
-        <v>90973</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,34 +1553,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517557</v>
+        <v>517546</v>
       </c>
       <c r="R10" t="n">
-        <v>6706166</v>
+        <v>6706147</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246612</v>
+        <v>121246704</v>
       </c>
       <c r="B2" t="n">
-        <v>90468</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517537</v>
+        <v>517530</v>
       </c>
       <c r="R2" t="n">
-        <v>6706121</v>
+        <v>6706114</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246733</v>
+        <v>121246714</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,24 +797,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517571</v>
+        <v>517557</v>
       </c>
       <c r="R3" t="n">
-        <v>6706187</v>
+        <v>6706166</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246653</v>
+        <v>121246552</v>
       </c>
       <c r="B4" t="n">
-        <v>97998</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,28 +907,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -939,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517528</v>
+        <v>517527</v>
       </c>
       <c r="R4" t="n">
-        <v>6706125</v>
+        <v>6706134</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246696</v>
+        <v>121246445</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,34 +1010,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517523</v>
+        <v>517546</v>
       </c>
       <c r="R5" t="n">
-        <v>6706120</v>
+        <v>6706147</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246714</v>
+        <v>121246733</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,28 +1125,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1159,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517557</v>
+        <v>517571</v>
       </c>
       <c r="R6" t="n">
-        <v>6706166</v>
+        <v>6706187</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1222,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246723</v>
+        <v>121246653</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>97998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,30 +1227,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517560</v>
+        <v>517528</v>
       </c>
       <c r="R7" t="n">
-        <v>6706160</v>
+        <v>6706125</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1328,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246552</v>
+        <v>121246723</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,31 +1338,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1372,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517527</v>
+        <v>517560</v>
       </c>
       <c r="R8" t="n">
-        <v>6706134</v>
+        <v>6706160</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1435,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246704</v>
+        <v>121246612</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>90468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,28 +1444,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1478,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517530</v>
+        <v>517537</v>
       </c>
       <c r="R9" t="n">
-        <v>6706114</v>
+        <v>6706121</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1541,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246445</v>
+        <v>121246696</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,35 +1554,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517546</v>
+        <v>517523</v>
       </c>
       <c r="R10" t="n">
-        <v>6706147</v>
+        <v>6706120</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246704</v>
+        <v>121246653</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517530</v>
+        <v>517528</v>
       </c>
       <c r="R2" t="n">
-        <v>6706114</v>
+        <v>6706125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246714</v>
+        <v>121246552</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517557</v>
+        <v>517527</v>
       </c>
       <c r="R3" t="n">
-        <v>6706166</v>
+        <v>6706134</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246552</v>
+        <v>121246704</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +905,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517527</v>
+        <v>517530</v>
       </c>
       <c r="R4" t="n">
-        <v>6706134</v>
+        <v>6706114</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246445</v>
+        <v>121246714</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,35 +1011,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517546</v>
+        <v>517557</v>
       </c>
       <c r="R5" t="n">
-        <v>6706147</v>
+        <v>6706166</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246733</v>
+        <v>121246445</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1121,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517571</v>
+        <v>517546</v>
       </c>
       <c r="R6" t="n">
-        <v>6706187</v>
+        <v>6706147</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246653</v>
+        <v>121246696</v>
       </c>
       <c r="B7" t="n">
-        <v>97998</v>
+        <v>90995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,35 +1232,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517528</v>
+        <v>517523</v>
       </c>
       <c r="R7" t="n">
-        <v>6706125</v>
+        <v>6706120</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1326,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246723</v>
+        <v>121246612</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>90480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,28 +1342,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1369,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517560</v>
+        <v>517537</v>
       </c>
       <c r="R8" t="n">
-        <v>6706160</v>
+        <v>6706121</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1432,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246612</v>
+        <v>121246723</v>
       </c>
       <c r="B9" t="n">
-        <v>90468</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,32 +1452,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517537</v>
+        <v>517560</v>
       </c>
       <c r="R9" t="n">
-        <v>6706121</v>
+        <v>6706160</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246696</v>
+        <v>121246733</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,28 +1562,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517523</v>
+        <v>517571</v>
       </c>
       <c r="R10" t="n">
-        <v>6706120</v>
+        <v>6706187</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246653</v>
+        <v>121246704</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517528</v>
+        <v>517530</v>
       </c>
       <c r="R2" t="n">
-        <v>6706125</v>
+        <v>6706114</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246552</v>
+        <v>121246612</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>90481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,27 +797,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517527</v>
+        <v>517537</v>
       </c>
       <c r="R3" t="n">
-        <v>6706134</v>
+        <v>6706121</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -893,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246704</v>
+        <v>121246445</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,30 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517530</v>
+        <v>517546</v>
       </c>
       <c r="R4" t="n">
-        <v>6706114</v>
+        <v>6706147</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246714</v>
+        <v>121246696</v>
       </c>
       <c r="B5" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1037,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517557</v>
+        <v>517523</v>
       </c>
       <c r="R5" t="n">
-        <v>6706166</v>
+        <v>6706120</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246445</v>
+        <v>121246733</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,35 +1124,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517546</v>
+        <v>517571</v>
       </c>
       <c r="R6" t="n">
-        <v>6706147</v>
+        <v>6706187</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1220,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246696</v>
+        <v>121246653</v>
       </c>
       <c r="B7" t="n">
-        <v>90995</v>
+        <v>98012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,34 +1230,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517523</v>
+        <v>517528</v>
       </c>
       <c r="R7" t="n">
-        <v>6706120</v>
+        <v>6706125</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1330,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246612</v>
+        <v>121246714</v>
       </c>
       <c r="B8" t="n">
-        <v>90480</v>
+        <v>90996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,30 +1341,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1377,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517537</v>
+        <v>517557</v>
       </c>
       <c r="R8" t="n">
-        <v>6706121</v>
+        <v>6706166</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1443,7 +1442,7 @@
         <v>121246723</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246733</v>
+        <v>121246552</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>97049</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,30 +1557,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517571</v>
+        <v>517527</v>
       </c>
       <c r="R10" t="n">
-        <v>6706187</v>
+        <v>6706134</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246704</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246612</v>
+        <v>121246653</v>
       </c>
       <c r="B3" t="n">
-        <v>90481</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,30 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517537</v>
+        <v>517528</v>
       </c>
       <c r="R3" t="n">
-        <v>6706121</v>
+        <v>6706125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246445</v>
+        <v>121246612</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>90484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +904,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517546</v>
+        <v>517537</v>
       </c>
       <c r="R4" t="n">
-        <v>6706147</v>
+        <v>6706121</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246696</v>
+        <v>121246552</v>
       </c>
       <c r="B5" t="n">
-        <v>90996</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,34 +1014,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517523</v>
+        <v>517527</v>
       </c>
       <c r="R5" t="n">
-        <v>6706120</v>
+        <v>6706134</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246733</v>
+        <v>121246445</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,30 +1121,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517571</v>
+        <v>517546</v>
       </c>
       <c r="R6" t="n">
-        <v>6706187</v>
+        <v>6706147</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1218,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246653</v>
+        <v>121246714</v>
       </c>
       <c r="B7" t="n">
-        <v>98012</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,35 +1232,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1266,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517528</v>
+        <v>517557</v>
       </c>
       <c r="R7" t="n">
-        <v>6706125</v>
+        <v>6706166</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1329,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246714</v>
+        <v>121246696</v>
       </c>
       <c r="B8" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,7 +1365,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1376,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517557</v>
+        <v>517523</v>
       </c>
       <c r="R8" t="n">
-        <v>6706166</v>
+        <v>6706120</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1442,7 +1443,7 @@
         <v>121246723</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246552</v>
+        <v>121246733</v>
       </c>
       <c r="B10" t="n">
-        <v>97049</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,31 +1558,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517527</v>
+        <v>517571</v>
       </c>
       <c r="R10" t="n">
-        <v>6706134</v>
+        <v>6706187</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246653</v>
+        <v>121246714</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517528</v>
+        <v>517557</v>
       </c>
       <c r="R3" t="n">
-        <v>6706125</v>
+        <v>6706166</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -892,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246612</v>
+        <v>121246733</v>
       </c>
       <c r="B4" t="n">
-        <v>90484</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,32 +903,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517537</v>
+        <v>517571</v>
       </c>
       <c r="R4" t="n">
-        <v>6706121</v>
+        <v>6706187</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246552</v>
+        <v>121246653</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,24 +1013,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1046,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517527</v>
+        <v>517528</v>
       </c>
       <c r="R5" t="n">
-        <v>6706134</v>
+        <v>6706125</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246445</v>
+        <v>121246552</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>97052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,32 +1120,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1157,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517546</v>
+        <v>517527</v>
       </c>
       <c r="R6" t="n">
-        <v>6706147</v>
+        <v>6706134</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246714</v>
+        <v>121246445</v>
       </c>
       <c r="B7" t="n">
-        <v>90999</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,34 +1227,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517557</v>
+        <v>517546</v>
       </c>
       <c r="R7" t="n">
-        <v>6706166</v>
+        <v>6706147</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1546,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246733</v>
+        <v>121246612</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>90484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,28 +1554,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517571</v>
+        <v>517537</v>
       </c>
       <c r="R10" t="n">
-        <v>6706187</v>
+        <v>6706121</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246704</v>
+        <v>121246653</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517530</v>
+        <v>517528</v>
       </c>
       <c r="R2" t="n">
-        <v>6706114</v>
+        <v>6706125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246714</v>
+        <v>121246445</v>
       </c>
       <c r="B3" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517557</v>
+        <v>517546</v>
       </c>
       <c r="R3" t="n">
-        <v>6706166</v>
+        <v>6706147</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246733</v>
+        <v>121246612</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +909,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517571</v>
+        <v>517537</v>
       </c>
       <c r="R4" t="n">
-        <v>6706187</v>
+        <v>6706121</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246653</v>
+        <v>121246696</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>91005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,35 +1019,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517528</v>
+        <v>517523</v>
       </c>
       <c r="R5" t="n">
-        <v>6706125</v>
+        <v>6706120</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,7 +1120,7 @@
         <v>121246552</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246445</v>
+        <v>121246714</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,35 +1236,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517546</v>
+        <v>517557</v>
       </c>
       <c r="R7" t="n">
-        <v>6706147</v>
+        <v>6706166</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1326,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246696</v>
+        <v>121246733</v>
       </c>
       <c r="B8" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,28 +1350,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517523</v>
+        <v>517571</v>
       </c>
       <c r="R8" t="n">
-        <v>6706120</v>
+        <v>6706187</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1436,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246723</v>
+        <v>121246704</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517560</v>
+        <v>517530</v>
       </c>
       <c r="R9" t="n">
-        <v>6706160</v>
+        <v>6706114</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246612</v>
+        <v>121246723</v>
       </c>
       <c r="B10" t="n">
-        <v>90484</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,32 +1558,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517537</v>
+        <v>517560</v>
       </c>
       <c r="R10" t="n">
-        <v>6706121</v>
+        <v>6706160</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246696</v>
+        <v>121246552</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>97058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,34 +1019,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517523</v>
+        <v>517527</v>
       </c>
       <c r="R5" t="n">
-        <v>6706120</v>
+        <v>6706134</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246552</v>
+        <v>121246696</v>
       </c>
       <c r="B6" t="n">
-        <v>97058</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,31 +1126,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517527</v>
+        <v>517523</v>
       </c>
       <c r="R6" t="n">
-        <v>6706134</v>
+        <v>6706120</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246653</v>
+        <v>121246696</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517528</v>
+        <v>517523</v>
       </c>
       <c r="R2" t="n">
-        <v>6706125</v>
+        <v>6706120</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246445</v>
+        <v>121246653</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517546</v>
+        <v>517528</v>
       </c>
       <c r="R3" t="n">
-        <v>6706147</v>
+        <v>6706125</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -900,7 +899,7 @@
         <v>121246612</v>
       </c>
       <c r="B4" t="n">
-        <v>90490</v>
+        <v>90491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1007,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246552</v>
+        <v>121246723</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,31 +1018,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517527</v>
+        <v>517560</v>
       </c>
       <c r="R5" t="n">
-        <v>6706134</v>
+        <v>6706160</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246696</v>
+        <v>121246445</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,34 +1124,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517523</v>
+        <v>517546</v>
       </c>
       <c r="R6" t="n">
-        <v>6706120</v>
+        <v>6706147</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1224,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246714</v>
+        <v>121246733</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,28 +1239,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1271,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517557</v>
+        <v>517571</v>
       </c>
       <c r="R7" t="n">
-        <v>6706166</v>
+        <v>6706187</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1334,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246733</v>
+        <v>121246552</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,30 +1341,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517571</v>
+        <v>517527</v>
       </c>
       <c r="R8" t="n">
-        <v>6706187</v>
+        <v>6706134</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1443,7 +1439,7 @@
         <v>121246704</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246723</v>
+        <v>121246714</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>91006</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,24 +1558,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517560</v>
+        <v>517557</v>
       </c>
       <c r="R10" t="n">
-        <v>6706160</v>
+        <v>6706166</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246696</v>
+        <v>121246653</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517523</v>
+        <v>517528</v>
       </c>
       <c r="R2" t="n">
-        <v>6706120</v>
+        <v>6706125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246653</v>
+        <v>121246704</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517528</v>
+        <v>517530</v>
       </c>
       <c r="R3" t="n">
-        <v>6706125</v>
+        <v>6706114</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246612</v>
+        <v>121246714</v>
       </c>
       <c r="B4" t="n">
-        <v>90491</v>
+        <v>91006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517537</v>
+        <v>517557</v>
       </c>
       <c r="R4" t="n">
-        <v>6706121</v>
+        <v>6706166</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246723</v>
+        <v>121246552</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,30 +1014,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517560</v>
+        <v>517527</v>
       </c>
       <c r="R5" t="n">
-        <v>6706160</v>
+        <v>6706134</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246445</v>
+        <v>121246696</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,35 +1121,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517546</v>
+        <v>517523</v>
       </c>
       <c r="R6" t="n">
-        <v>6706147</v>
+        <v>6706120</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1223,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246733</v>
+        <v>121246723</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517571</v>
+        <v>517560</v>
       </c>
       <c r="R7" t="n">
-        <v>6706187</v>
+        <v>6706160</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1329,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246552</v>
+        <v>121246445</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,28 +1337,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517527</v>
+        <v>517546</v>
       </c>
       <c r="R8" t="n">
-        <v>6706134</v>
+        <v>6706147</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246704</v>
+        <v>121246733</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517530</v>
+        <v>517571</v>
       </c>
       <c r="R9" t="n">
-        <v>6706114</v>
+        <v>6706187</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246714</v>
+        <v>121246612</v>
       </c>
       <c r="B10" t="n">
-        <v>91006</v>
+        <v>90491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,30 +1554,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517557</v>
+        <v>517537</v>
       </c>
       <c r="R10" t="n">
-        <v>6706166</v>
+        <v>6706121</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246653</v>
+        <v>121246723</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517528</v>
+        <v>517560</v>
       </c>
       <c r="R2" t="n">
-        <v>6706125</v>
+        <v>6706160</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246552</v>
+        <v>121246653</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,24 +1013,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1046,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517527</v>
+        <v>517528</v>
       </c>
       <c r="R5" t="n">
-        <v>6706134</v>
+        <v>6706125</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246696</v>
+        <v>121246445</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,34 +1120,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517523</v>
+        <v>517546</v>
       </c>
       <c r="R6" t="n">
-        <v>6706120</v>
+        <v>6706147</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246723</v>
+        <v>121246733</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517560</v>
+        <v>517571</v>
       </c>
       <c r="R7" t="n">
-        <v>6706160</v>
+        <v>6706187</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246445</v>
+        <v>121246612</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>90491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,35 +1337,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517546</v>
+        <v>517537</v>
       </c>
       <c r="R8" t="n">
-        <v>6706147</v>
+        <v>6706121</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1436,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246733</v>
+        <v>121246696</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,24 +1451,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1479,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517571</v>
+        <v>517523</v>
       </c>
       <c r="R9" t="n">
-        <v>6706187</v>
+        <v>6706120</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246612</v>
+        <v>121246552</v>
       </c>
       <c r="B10" t="n">
-        <v>90491</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,30 +1561,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517537</v>
+        <v>517527</v>
       </c>
       <c r="R10" t="n">
-        <v>6706121</v>
+        <v>6706134</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 52435-2024 artfynd.xlsx
+++ b/artfynd/A 52435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246723</v>
+        <v>121246733</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517560</v>
+        <v>517571</v>
       </c>
       <c r="R2" t="n">
-        <v>6706160</v>
+        <v>6706187</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246704</v>
+        <v>121246612</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>90491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,28 +793,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517530</v>
+        <v>517537</v>
       </c>
       <c r="R3" t="n">
-        <v>6706114</v>
+        <v>6706121</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246714</v>
+        <v>121246723</v>
       </c>
       <c r="B4" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +907,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517557</v>
+        <v>517560</v>
       </c>
       <c r="R4" t="n">
-        <v>6706166</v>
+        <v>6706160</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246445</v>
+        <v>121246696</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,35 +1120,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517546</v>
+        <v>517523</v>
       </c>
       <c r="R6" t="n">
-        <v>6706147</v>
+        <v>6706120</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1219,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246733</v>
+        <v>121246704</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517571</v>
+        <v>517530</v>
       </c>
       <c r="R7" t="n">
-        <v>6706187</v>
+        <v>6706114</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1325,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246612</v>
+        <v>121246714</v>
       </c>
       <c r="B8" t="n">
-        <v>90491</v>
+        <v>91006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,30 +1336,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1372,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517537</v>
+        <v>517557</v>
       </c>
       <c r="R8" t="n">
-        <v>6706121</v>
+        <v>6706166</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1435,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246696</v>
+        <v>121246445</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,34 +1446,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517523</v>
+        <v>517546</v>
       </c>
       <c r="R9" t="n">
-        <v>6706120</v>
+        <v>6706147</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
